--- a/isolated_excel/Table 4 - Paper vs Current.xlsx
+++ b/isolated_excel/Table 4 - Paper vs Current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparison'!$A$1:$D$11</definedName>

--- a/isolated_excel/Table 4 - Paper vs Current.xlsx
+++ b/isolated_excel/Table 4 - Paper vs Current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparison'!$A$1:$D$11</definedName>
@@ -478,10 +478,10 @@
         <v>3.47</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3.495221238938055</v>
+        <v>3.520614035087721</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.02522123893805484</v>
+        <v>0.05061403508772111</v>
       </c>
     </row>
     <row r="3">
@@ -494,10 +494,10 @@
         <v>3.4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.422856966733567</v>
+        <v>3.448521353622169</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.02285696673356741</v>
+        <v>0.04852135362216936</v>
       </c>
     </row>
     <row r="4">
@@ -510,10 +510,10 @@
         <v>95.41</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>95.57522123893806</v>
+        <v>95.6140350877193</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.1652212389380594</v>
+        <v>0.2040350877193049</v>
       </c>
     </row>
     <row r="5">
@@ -526,10 +526,10 @@
         <v>4.59</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4.424778761061947</v>
+        <v>4.385964912280701</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.1652212389380532</v>
+        <v>-0.2040350877192987</v>
       </c>
     </row>
     <row r="6">
@@ -542,10 +542,10 @@
         <v>3.68</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.697222222222224</v>
+        <v>3.721926605504589</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.01722222222222358</v>
+        <v>0.04192660550458838</v>
       </c>
     </row>
     <row r="7">
@@ -574,10 +574,10 @@
         <v>4.06</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4.010102220229272</v>
+        <v>4.001514378174758</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-0.04989777977072762</v>
+        <v>-0.0584856218252412</v>
       </c>
     </row>
     <row r="9">
@@ -590,10 +590,10 @@
         <v>0.86</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.8716040257792284</v>
+        <v>0.8798204135639283</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.01160402577922837</v>
+        <v>0.01982041356392827</v>
       </c>
     </row>
     <row r="10">
@@ -606,10 +606,10 @@
         <v>13.96</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>14.35776078315886</v>
+        <v>14.52592048115421</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.3977607831588568</v>
+        <v>0.5659204811542047</v>
       </c>
     </row>
     <row r="11">
@@ -622,10 +622,10 @@
         <v>88.28</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>92.0046082949309</v>
+        <v>93.47695852534564</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3.724608294930903</v>
+        <v>5.196958525345636</v>
       </c>
     </row>
   </sheetData>
@@ -679,7 +679,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to May 2026; 113 monthly observations</t>
+          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 4 - Paper vs Current.xlsx
+++ b/isolated_excel/Table 4 - Paper vs Current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparison'!$A$1:$D$11</definedName>
@@ -442,7 +442,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -478,10 +478,10 @@
         <v>3.47</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3.520614035087721</v>
+        <v>3.519478260869565</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.05061403508772111</v>
+        <v>0.04947826086956475</v>
       </c>
     </row>
     <row r="3">
@@ -494,10 +494,10 @@
         <v>3.4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.448521353622169</v>
+        <v>3.448012329545969</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.04852135362216936</v>
+        <v>0.04801232954596868</v>
       </c>
     </row>
     <row r="4">
@@ -510,10 +510,10 @@
         <v>95.41</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>95.6140350877193</v>
+        <v>95.65217391304348</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.2040350877193049</v>
+        <v>0.2421739130434872</v>
       </c>
     </row>
     <row r="5">
@@ -526,10 +526,10 @@
         <v>4.59</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4.385964912280701</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.2040350877192987</v>
+        <v>-0.2421739130434784</v>
       </c>
     </row>
     <row r="6">
@@ -542,10 +542,10 @@
         <v>3.68</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.721926605504589</v>
+        <v>3.718909090909091</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.04192660550458838</v>
+        <v>0.03890909090909078</v>
       </c>
     </row>
     <row r="7">
@@ -558,10 +558,10 @@
         <v>-0.87</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-0.8680000000000002</v>
+        <v>-0.868</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.00199999999999978</v>
+        <v>0.002000000000000002</v>
       </c>
     </row>
     <row r="8">
@@ -574,10 +574,10 @@
         <v>4.06</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4.001514378174758</v>
+        <v>3.983943837120484</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-0.0584856218252412</v>
+        <v>-0.076056162879516</v>
       </c>
     </row>
     <row r="9">
@@ -590,10 +590,10 @@
         <v>0.86</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.8798204135639283</v>
+        <v>0.8834156315349503</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.01982041356392827</v>
+        <v>0.0234156315349503</v>
       </c>
     </row>
     <row r="10">
@@ -606,10 +606,10 @@
         <v>13.96</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>14.52592048115421</v>
+        <v>14.58478488287688</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.5659204811542047</v>
+        <v>0.6247848828768756</v>
       </c>
     </row>
     <row r="11">
@@ -622,10 +622,10 @@
         <v>88.28</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>93.47695852534564</v>
+        <v>94.25806451612902</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.196958525345636</v>
+        <v>5.978064516129024</v>
       </c>
     </row>
   </sheetData>
@@ -679,7 +679,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
+          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 4 - Paper vs Current.xlsx
+++ b/isolated_excel/Table 4 - Paper vs Current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparison'!$A$1:$D$11</definedName>
@@ -442,7 +442,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -478,10 +478,10 @@
         <v>3.47</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3.519478260869565</v>
+        <v>3.519478260869567</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.04947826086956475</v>
+        <v>0.04947826086956697</v>
       </c>
     </row>
     <row r="3">
@@ -542,10 +542,10 @@
         <v>3.68</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.718909090909091</v>
+        <v>3.718909090909092</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.03890909090909078</v>
+        <v>0.03890909090909211</v>
       </c>
     </row>
     <row r="7">
@@ -558,10 +558,10 @@
         <v>-0.87</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-0.868</v>
+        <v>-0.8680000000000002</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.00199999999999978</v>
       </c>
     </row>
     <row r="8">
@@ -590,10 +590,10 @@
         <v>0.86</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.8834156315349503</v>
+        <v>0.8834156315349508</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.0234156315349503</v>
+        <v>0.02341563153495085</v>
       </c>
     </row>
     <row r="10">
@@ -606,10 +606,10 @@
         <v>13.96</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>14.58478488287688</v>
+        <v>14.58478488287689</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.6247848828768756</v>
+        <v>0.6247848828768845</v>
       </c>
     </row>
     <row r="11">
@@ -622,10 +622,10 @@
         <v>88.28</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>94.25806451612902</v>
+        <v>94.25806451612905</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.978064516129024</v>
+        <v>5.978064516129052</v>
       </c>
     </row>
   </sheetData>
